--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488060_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488060_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.371600000000001</v>
+        <v>10.1262</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9584</v>
+        <v>5.9376</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4132</v>
+        <v>4.1886</v>
       </c>
       <c r="G2" t="n">
         <v>8.9693</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3628</v>
+        <v>0.3918</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9873</v>
+        <v>-0.0081</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.3999</v>
       </c>
       <c r="V2" t="n">
         <v>2.1527</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.317</v>
+        <v>5.4897</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3286</v>
+        <v>3.3328</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9884</v>
+        <v>2.1569</v>
       </c>
       <c r="G3" t="n">
         <v>3.9294</v>
@@ -688,13 +688,13 @@
         <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4816</v>
+        <v>0.6543</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6668</v>
+        <v>0.671</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1852</v>
+        <v>-0.0167</v>
       </c>
       <c r="V3" t="n">
         <v>2.2935</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.872</v>
+        <v>1.2639</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4281</v>
+        <v>-0.8958</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.1596</v>
       </c>
       <c r="G4" t="n">
         <v>0.2186</v>
@@ -766,13 +766,13 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.3405</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9984</v>
+        <v>-0.4661</v>
       </c>
       <c r="U4" t="n">
-        <v>0.266</v>
+        <v>0.1256</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7947</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>P. IBÁÑEZ FIDALGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.3027</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6501</v>
+        <v>0.3027</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2877</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2386</v>
+        <v>0.3027</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7264</v>
+        <v>0.3027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4878</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5181</v>
+        <v>0.3027</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5984</v>
+        <v>0.3027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.128</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4075</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2815</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8591</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4224</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4153</v>
+        <v>-0.1378</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.182</v>
+        <v>-0.5665</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5972</v>
+        <v>0.4288</v>
       </c>
       <c r="G6" t="n">
         <v>0.6931</v>
@@ -922,13 +922,13 @@
         <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>1.066</v>
+        <v>0.513</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4847</v>
+        <v>0.1001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5813</v>
+        <v>0.4128</v>
       </c>
       <c r="V6" t="n">
         <v>-1.7403</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. IBÁÑEZ FIDALGO</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3027</v>
+        <v>-0.1639</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3027</v>
+        <v>-1.1989</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.035</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3027</v>
+        <v>-0.2386</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3027</v>
+        <v>-0.7264</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.4878</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3027</v>
+        <v>-0.5181</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3027</v>
+        <v>-0.5984</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.4075</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1697</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2901</v>
+        <v>-0.1996</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0422</v>
+        <v>0.0202</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2479</v>
+        <v>-0.2198</v>
       </c>
       <c r="G8" t="n">
         <v>0.156</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1795</v>
+        <v>-0.089</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0624</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. CASTRO BRAVO</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7987</v>
+        <v>-0.6055</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4142</v>
+        <v>-1.1176</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.213</v>
+        <v>0.5121</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0862</v>
+        <v>-1.1423</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5945</v>
+        <v>1.5034</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4917</v>
+        <v>-2.6458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0471</v>
+        <v>-0.6625</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0069</v>
+        <v>1.4799</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0402</v>
+        <v>-2.1424</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1333</v>
+        <v>-0.4798</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6014</v>
+        <v>0.0235</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5319</v>
+        <v>-0.5034</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2875</v>
+        <v>0.1927</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3671</v>
+        <v>0.0534</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.1393</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1459</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>S. CASTRO BRAVO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5163</v>
+        <v>-0.8558</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.916</v>
+        <v>0.2729</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3997</v>
+        <v>-1.1287</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1423</v>
+        <v>-1.0862</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5034</v>
+        <v>-0.5945</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6458</v>
+        <v>-0.4917</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6625</v>
+        <v>0.0471</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4799</v>
+        <v>0.0069</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1424</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4798</v>
+        <v>-1.1333</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0235</v>
+        <v>-0.6014</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5034</v>
+        <v>-0.5319</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.718</v>
+        <v>0.2304</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.745</v>
+        <v>0.2258</v>
       </c>
       <c r="U10" t="n">
-        <v>0.027</v>
+        <v>0.0046</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1459</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0051</v>
+        <v>-1.5519</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.648</v>
+        <v>-1.1387</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3571</v>
+        <v>-0.4132</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3017</v>
@@ -1312,13 +1312,13 @@
         <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4948</v>
+        <v>0.948</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2534</v>
+        <v>0.7627</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2415</v>
+        <v>0.1853</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0101</v>
+        <v>-3.5297</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5535</v>
+        <v>-2.7776</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4566</v>
+        <v>-0.7521</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8001</v>
+        <v>-2.3063</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1432</v>
+        <v>-1.7648</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6569</v>
+        <v>-0.5415</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4949</v>
+        <v>-1.7958</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8961</v>
+        <v>-1.2372</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5988</v>
+        <v>-0.5586</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3052</v>
+        <v>-0.5105</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7529</v>
+        <v>-0.5276</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0581</v>
+        <v>0.0171</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5231</v>
+        <v>-0.155</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9325</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4094</v>
+        <v>-0.1644</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9314</v>
+        <v>-0.8701</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.9314</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1671</v>
+        <v>-4.0734</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1061</v>
+        <v>-2.7573</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.061</v>
+        <v>-1.3162</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.3063</v>
+        <v>-2.8001</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7648</v>
+        <v>-1.1432</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5415</v>
+        <v>-1.6569</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7958</v>
+        <v>-2.4949</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2372</v>
+        <v>-1.8961</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5586</v>
+        <v>-0.5988</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5105</v>
+        <v>-0.3052</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5276</v>
+        <v>0.7529</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0171</v>
+        <v>-1.0581</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1982</v>
+        <v>0.1982</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7924</v>
+        <v>0.4598</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3192</v>
+        <v>0.7288</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4732</v>
+        <v>-0.269</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8701</v>
+        <v>-1.9314</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8701</v>
+        <v>-1.9314</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1288</v>
+        <v>6.064900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.522100000000001</v>
+        <v>-0.5861999999999994</v>
       </c>
       <c r="F14" t="n">
-        <v>6.650599999999999</v>
+        <v>6.650999999999998</v>
       </c>
       <c r="G14" t="n">
         <v>4.393899999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>8.440099999999999</v>
+        <v>8.440100000000003</v>
       </c>
       <c r="I14" t="n">
         <v>-4.0464</v>
@@ -1522,22 +1522,22 @@
         <v>4.735900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.623700000000001</v>
+        <v>7.6237</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.8875</v>
+        <v>-2.887499999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3423000000000002</v>
+        <v>-0.3422999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8163999999999999</v>
+        <v>0.8164</v>
       </c>
       <c r="O14" t="n">
         <v>-1.1588</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0001000000000001</v>
+        <v>-0.0001000000000000445</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.8667</v>
@@ -1546,22 +1546,22 @@
         <v>14.8668</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3494</v>
+        <v>3.2855</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4513</v>
+        <v>2.3872</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8980999999999999</v>
+        <v>0.8981</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.614600000000001</v>
+        <v>-1.6146</v>
       </c>
       <c r="W14" t="n">
         <v>7.1571</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.771700000000001</v>
+        <v>-8.771699999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>H. TAVIO SOLIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3341</v>
+        <v>0.9949</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1054</v>
+        <v>1.4985</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2286</v>
+        <v>-0.5036</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6569</v>
+        <v>1.4665</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5079</v>
+        <v>-0.066</v>
       </c>
       <c r="I16" t="n">
-        <v>0.149</v>
+        <v>1.5325</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9592</v>
+        <v>1.5792</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8387</v>
+        <v>0.3298</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1205</v>
+        <v>1.2494</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3023</v>
+        <v>-0.1126</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3308</v>
+        <v>-0.3957</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0285</v>
+        <v>0.2831</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.1627</v>
+        <v>0.7929</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.9467</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0917</v>
+        <v>-0.1248</v>
       </c>
       <c r="T16" t="n">
-        <v>1.542</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5496</v>
+        <v>-0.0441</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7482</v>
+        <v>-1.1397</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5509</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8027</v>
+        <v>-1.1397</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. TAVIO SOLIS</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3628</v>
+        <v>0.605</v>
       </c>
       <c r="E17" t="n">
-        <v>1.091</v>
+        <v>1.6846</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7282</v>
+        <v>-1.0796</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4665</v>
+        <v>1.4224</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.066</v>
+        <v>0.066</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5325</v>
+        <v>1.3564</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5792</v>
+        <v>1.9194</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3298</v>
+        <v>1.2648</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2494</v>
+        <v>0.6545</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1126</v>
+        <v>-0.497</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3957</v>
+        <v>-1.1989</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2831</v>
+        <v>0.7019</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7929</v>
+        <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7569</v>
+        <v>-0.3854</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4881</v>
+        <v>-0.0365</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2688</v>
+        <v>-0.3489</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1397</v>
+        <v>-2.4142</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1397</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. LOPEZ TORRE</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0987</v>
+        <v>0.571</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5174</v>
+        <v>0.6793</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6161</v>
+        <v>-0.1083</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1199</v>
+        <v>1.6569</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0217</v>
+        <v>1.5079</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1415</v>
+        <v>0.149</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0404</v>
+        <v>2.9592</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0404</v>
+        <v>2.8387</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1205</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0795</v>
+        <v>-1.3023</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.062</v>
+        <v>-1.3308</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1415</v>
+        <v>0.0285</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5947</v>
+        <v>-4.1627</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>-5.9467</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2966</v>
+        <v>0.3285</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4368</v>
+        <v>0.1158</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1402</v>
+        <v>0.2127</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8701</v>
+        <v>2.7482</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8701</v>
+        <v>3.5509</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.8027</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>G. LOPEZ TORRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.336</v>
+        <v>0.1549</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4413</v>
+        <v>-0.5174</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1053</v>
+        <v>0.6723</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5623</v>
+        <v>0.1199</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0418</v>
+        <v>-0.0217</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5205</v>
+        <v>0.1415</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3499</v>
+        <v>0.0404</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3499</v>
+        <v>0.0404</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9123</v>
+        <v>0.0795</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3918</v>
+        <v>-0.062</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5205</v>
+        <v>0.1415</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5947</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1097</v>
+        <v>-0.2405</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8001</v>
+        <v>-0.4368</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3095</v>
+        <v>0.1963</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.8701</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7413999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5064</v>
+        <v>-0.0376</v>
       </c>
       <c r="E20" t="n">
-        <v>0.182</v>
+        <v>-1.3394</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6884</v>
+        <v>1.3019</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6827</v>
+        <v>-0.5623</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3327</v>
+        <v>-0.0418</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3499</v>
+        <v>-0.5205</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3294</v>
+        <v>0.3499</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1299</v>
+        <v>0.3499</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4593</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3533</v>
+        <v>-0.9123</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4627</v>
+        <v>-0.3918</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1094</v>
+        <v>-0.5205</v>
       </c>
       <c r="P20" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.5858</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.1982</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.784</v>
-      </c>
       <c r="S20" t="n">
-        <v>-0.5394</v>
+        <v>-0.8113</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1011</v>
+        <v>-0.6983</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5617</v>
+        <v>-0.113</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8701</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.6808</v>
+        <v>0.7413999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.795</v>
+        <v>-0.0891</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8696</v>
+        <v>0.9969</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6647</v>
+        <v>-1.086</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4224</v>
+        <v>-0.6827</v>
       </c>
       <c r="H21" t="n">
-        <v>0.066</v>
+        <v>-0.3327</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3564</v>
+        <v>-0.3499</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9194</v>
+        <v>-0.3294</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2648</v>
+        <v>1.1299</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6545</v>
+        <v>-1.4593</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.497</v>
+        <v>-0.3533</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1989</v>
+        <v>-1.4627</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7019</v>
+        <v>1.1094</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7855</v>
+        <v>-0.1221</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8515</v>
+        <v>-0.2861</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9340000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4142</v>
+        <v>-0.8701</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4142</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. WRIGHT RODRIGUEZ</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0879</v>
+        <v>-2.159</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.133</v>
+        <v>-3.7287</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0451</v>
+        <v>1.5698</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3436</v>
+        <v>-1.5742</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6516</v>
+        <v>-1.7121</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3079</v>
+        <v>0.1379</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.231</v>
+        <v>-1.5432</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3917</v>
+        <v>-0.7189</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1607</v>
+        <v>-0.8243</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1126</v>
+        <v>-0.031</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2599</v>
+        <v>-0.9932</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1472</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9822</v>
+        <v>0.1982</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1716</v>
+        <v>-2.1805</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1893</v>
+        <v>2.3787</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1706</v>
+        <v>-0.446</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9435</v>
+        <v>0.0653</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2271</v>
+        <v>-0.5113</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0674</v>
+        <v>-0.337</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.674</v>
+        <v>-0.0704</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7413999999999999</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>D. WRIGHT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5371</v>
+        <v>-2.974</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8306</v>
+        <v>-4.8461</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2936</v>
+        <v>1.8721</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5742</v>
+        <v>-1.3436</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7121</v>
+        <v>-1.6516</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1379</v>
+        <v>0.3079</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5432</v>
+        <v>-1.231</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7189</v>
+        <v>-1.3917</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8243</v>
+        <v>0.1607</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.031</v>
+        <v>-0.1126</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9932</v>
+        <v>-0.2599</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.1472</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1982</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1805</v>
+        <v>-3.1716</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3787</v>
+        <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8241000000000001</v>
+        <v>0.2845</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0365</v>
+        <v>0.2305</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7875</v>
+        <v>0.054</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.337</v>
+        <v>0.0674</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0704</v>
+        <v>-0.674</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2666</v>
+        <v>0.7413999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6805</v>
+        <v>-4.5343</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2024</v>
+        <v>-5.3042</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5218</v>
+        <v>0.77</v>
       </c>
       <c r="G24" t="n">
         <v>-7.9153</v>
@@ -2326,13 +2326,13 @@
         <v>2.7751</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2995</v>
+        <v>-0.1532</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3306</v>
+        <v>0.2287</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6301</v>
+        <v>-0.382</v>
       </c>
       <c r="V24" t="n">
         <v>1.9485</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1286</v>
+        <v>-4.4495</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.858000000000001</v>
+        <v>-7.857799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>2.729200000000001</v>
+        <v>3.4086</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3937</v>
+        <v>-4.393700000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-8.44</v>
@@ -2377,25 +2377,25 @@
         <v>4.046200000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3423000000000007</v>
+        <v>0.3423000000000016</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8163999999999998</v>
+        <v>-0.8164000000000007</v>
       </c>
       <c r="L25" t="n">
-        <v>1.1587</v>
+        <v>1.158700000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-4.736</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.6236</v>
+        <v>-7.623600000000001</v>
       </c>
       <c r="O25" t="n">
         <v>2.8875</v>
       </c>
       <c r="P25" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.8667</v>
@@ -2404,19 +2404,19 @@
         <v>14.8667</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.3494</v>
+        <v>-1.6703</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8980000000000001</v>
+        <v>-0.8981000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4513</v>
+        <v>-0.7723</v>
       </c>
       <c r="V25" t="n">
         <v>1.6146</v>
       </c>
       <c r="W25" t="n">
-        <v>7.564500000000001</v>
+        <v>7.564499999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-5.95</v>
